--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/167.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/167.xlsx
@@ -426,13 +426,13 @@
         <v>-16.30726494417638</v>
       </c>
       <c r="E2">
-        <v>-5.933910635028493</v>
+        <v>-6.244663578382848</v>
       </c>
       <c r="F2">
-        <v>-5.990608239998043</v>
+        <v>-4.945486909112407</v>
       </c>
       <c r="G2">
-        <v>-1.858690390964445</v>
+        <v>-4.428408670548605</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.99183788280329</v>
       </c>
       <c r="E3">
-        <v>-6.536895063045832</v>
+        <v>-7.3178394626166</v>
       </c>
       <c r="F3">
-        <v>-5.053817484580915</v>
+        <v>-5.015749032217861</v>
       </c>
       <c r="G3">
-        <v>-2.802490508209729</v>
+        <v>-4.821903423891918</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.52744156575297</v>
       </c>
       <c r="E4">
-        <v>-6.274143944172782</v>
+        <v>-7.506966651072945</v>
       </c>
       <c r="F4">
-        <v>-5.017483633559324</v>
+        <v>-4.853804861705363</v>
       </c>
       <c r="G4">
-        <v>-3.300207856220377</v>
+        <v>-4.113837322861517</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.9608833005156</v>
       </c>
       <c r="E5">
-        <v>-9.594538826920887</v>
+        <v>-8.581546362249075</v>
       </c>
       <c r="F5">
-        <v>-5.193040365602025</v>
+        <v>-4.464970859566081</v>
       </c>
       <c r="G5">
-        <v>-2.878444354517228</v>
+        <v>-3.278493988028298</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.30223747423968</v>
       </c>
       <c r="E6">
-        <v>-11.05876655561301</v>
+        <v>-9.884220780717554</v>
       </c>
       <c r="F6">
-        <v>-5.518379177949322</v>
+        <v>-4.716255282837908</v>
       </c>
       <c r="G6">
-        <v>-2.111483648343194</v>
+        <v>-4.92236854937218</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.58746994872165</v>
       </c>
       <c r="E7">
-        <v>-8.915240554926289</v>
+        <v>-11.44677979401223</v>
       </c>
       <c r="F7">
-        <v>-5.448630642633605</v>
+        <v>-4.813093088959976</v>
       </c>
       <c r="G7">
-        <v>-2.656415996834927</v>
+        <v>-4.82380036648592</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.84722958032951</v>
       </c>
       <c r="E8">
-        <v>-11.04767632276822</v>
+        <v>-12.09912006023916</v>
       </c>
       <c r="F8">
-        <v>-4.788691870375711</v>
+        <v>-4.523495016573866</v>
       </c>
       <c r="G8">
-        <v>-2.374268132159462</v>
+        <v>-4.516383107709197</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.09544546368443</v>
       </c>
       <c r="E9">
-        <v>-12.89247247859095</v>
+        <v>-12.58071421400689</v>
       </c>
       <c r="F9">
-        <v>-5.501667693965246</v>
+        <v>-4.65573890222639</v>
       </c>
       <c r="G9">
-        <v>-1.904286534676828</v>
+        <v>-3.983719640986003</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.34820771970094</v>
       </c>
       <c r="E10">
-        <v>-13.18478094731206</v>
+        <v>-13.91172782281537</v>
       </c>
       <c r="F10">
-        <v>-4.725135381395919</v>
+        <v>-4.605591196395713</v>
       </c>
       <c r="G10">
-        <v>-2.402391216515571</v>
+        <v>-3.215957782791464</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.63361020243758</v>
       </c>
       <c r="E11">
-        <v>-14.55488434375475</v>
+        <v>-16.47712193358265</v>
       </c>
       <c r="F11">
-        <v>-5.262016034130932</v>
+        <v>-4.687398275993985</v>
       </c>
       <c r="G11">
-        <v>-1.597448621369478</v>
+        <v>-3.719706944774665</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.956547082067882</v>
       </c>
       <c r="E12">
-        <v>-14.95612072625637</v>
+        <v>-14.93896233824131</v>
       </c>
       <c r="F12">
-        <v>-4.492671465515697</v>
+        <v>-4.435078393468658</v>
       </c>
       <c r="G12">
-        <v>-0.9863417780932521</v>
+        <v>-2.976565613755687</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.326025330542503</v>
       </c>
       <c r="E13">
-        <v>-15.41414417281417</v>
+        <v>-16.96659563212372</v>
       </c>
       <c r="F13">
-        <v>-4.312695393379059</v>
+        <v>-4.489229598957064</v>
       </c>
       <c r="G13">
-        <v>-1.226528478058455</v>
+        <v>-2.136369019161895</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.77092975415759</v>
       </c>
       <c r="E14">
-        <v>-17.71266172488741</v>
+        <v>-18.37116524423879</v>
       </c>
       <c r="F14">
-        <v>-4.724846281172342</v>
+        <v>-4.567983316308617</v>
       </c>
       <c r="G14">
-        <v>-0.7230209858996219</v>
+        <v>-1.243849252319922</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.295330271391013</v>
       </c>
       <c r="E15">
-        <v>-20.05121098718847</v>
+        <v>-19.56748845063713</v>
       </c>
       <c r="F15">
-        <v>-4.579638445666006</v>
+        <v>-4.564773392622768</v>
       </c>
       <c r="G15">
-        <v>-0.4831454772151102</v>
+        <v>-0.3310523940499133</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.9019556768657</v>
       </c>
       <c r="E16">
-        <v>-19.33824351094684</v>
+        <v>-19.94122341049017</v>
       </c>
       <c r="F16">
-        <v>-4.540834403049265</v>
+        <v>-4.35414192801073</v>
       </c>
       <c r="G16">
-        <v>1.427933146239968</v>
+        <v>-0.2235523592986993</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.605382055300892</v>
       </c>
       <c r="E17">
-        <v>-19.02560672240529</v>
+        <v>-21.22494616523655</v>
       </c>
       <c r="F17">
-        <v>-4.266727629462909</v>
+        <v>-3.910423615231563</v>
       </c>
       <c r="G17">
-        <v>2.534900121479311</v>
+        <v>0.4700598999072427</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.39637016760082</v>
       </c>
       <c r="E18">
-        <v>-20.50384102120313</v>
+        <v>-22.11389466989025</v>
       </c>
       <c r="F18">
-        <v>-4.350374513062797</v>
+        <v>-3.817040929546572</v>
       </c>
       <c r="G18">
-        <v>2.736267364451019</v>
+        <v>0.7318545306072689</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.258747338618289</v>
       </c>
       <c r="E19">
-        <v>-22.01721627830049</v>
+        <v>-23.3468260601666</v>
       </c>
       <c r="F19">
-        <v>-4.633243757035967</v>
+        <v>-4.116599291583944</v>
       </c>
       <c r="G19">
-        <v>2.679845736825221</v>
+        <v>1.989623476251492</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.187599661753903</v>
       </c>
       <c r="E20">
-        <v>-21.18956066934061</v>
+        <v>-23.77360303607147</v>
       </c>
       <c r="F20">
-        <v>-4.050743254693979</v>
+        <v>-3.51161772629738</v>
       </c>
       <c r="G20">
-        <v>3.382734144632201</v>
+        <v>2.345642854090255</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.165207837942706</v>
       </c>
       <c r="E21">
-        <v>-23.23196131696204</v>
+        <v>-24.02401859174763</v>
       </c>
       <c r="F21">
-        <v>-4.291898401364374</v>
+        <v>-3.632165892589779</v>
       </c>
       <c r="G21">
-        <v>3.308438881639877</v>
+        <v>2.730844690857694</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.169359818110864</v>
       </c>
       <c r="E22">
-        <v>-22.67017241699248</v>
+        <v>-25.48049357293862</v>
       </c>
       <c r="F22">
-        <v>-3.642364752053046</v>
+        <v>-3.502770762435482</v>
       </c>
       <c r="G22">
-        <v>3.798760470915793</v>
+        <v>2.453920867043198</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.191697956149165</v>
       </c>
       <c r="E23">
-        <v>-25.12757147962483</v>
+        <v>-26.27941148584583</v>
       </c>
       <c r="F23">
-        <v>-3.818892330691829</v>
+        <v>-3.379749091078324</v>
       </c>
       <c r="G23">
-        <v>4.009542905401189</v>
+        <v>3.955703503296022</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.220320482150137</v>
       </c>
       <c r="E24">
-        <v>-24.56891175519457</v>
+        <v>-26.0171449136916</v>
       </c>
       <c r="F24">
-        <v>-3.416594873154846</v>
+        <v>-3.063365758722692</v>
       </c>
       <c r="G24">
-        <v>3.308528266369437</v>
+        <v>3.603537600464971</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.238944636601317</v>
       </c>
       <c r="E25">
-        <v>-24.66484747704707</v>
+        <v>-26.36170744398722</v>
       </c>
       <c r="F25">
-        <v>-2.91519733811875</v>
+        <v>-3.369148473424699</v>
       </c>
       <c r="G25">
-        <v>3.238258626752867</v>
+        <v>3.728027354923725</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.245923430066577</v>
       </c>
       <c r="E26">
-        <v>-24.26933055721714</v>
+        <v>-26.52630388874402</v>
       </c>
       <c r="F26">
-        <v>-2.961930513515087</v>
+        <v>-3.445968781258117</v>
       </c>
       <c r="G26">
-        <v>3.720956029651842</v>
+        <v>3.830237137903183</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.24219053161436</v>
       </c>
       <c r="E27">
-        <v>-23.79918891421481</v>
+        <v>-26.39813901737893</v>
       </c>
       <c r="F27">
-        <v>-3.438875471187945</v>
+        <v>-3.571589869525259</v>
       </c>
       <c r="G27">
-        <v>3.417021464782432</v>
+        <v>3.834934802023409</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.222549516886769</v>
       </c>
       <c r="E28">
-        <v>-25.55509565374098</v>
+        <v>-26.80665718608488</v>
       </c>
       <c r="F28">
-        <v>-2.501893362900771</v>
+        <v>-3.070778818610345</v>
       </c>
       <c r="G28">
-        <v>2.651755757924505</v>
+        <v>3.77769878019495</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.194747098252653</v>
       </c>
       <c r="E29">
-        <v>-24.04320120764412</v>
+        <v>-26.35216142077905</v>
       </c>
       <c r="F29">
-        <v>-3.471364040725741</v>
+        <v>-3.256102830699456</v>
       </c>
       <c r="G29">
-        <v>4.08049451739885</v>
+        <v>2.917946793100683</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.171380756907668</v>
       </c>
       <c r="E30">
-        <v>-24.24217329859314</v>
+        <v>-24.88481810196966</v>
       </c>
       <c r="F30">
-        <v>-3.328543560074273</v>
+        <v>-3.209354744689869</v>
       </c>
       <c r="G30">
-        <v>3.42484428389173</v>
+        <v>4.245955583451623</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.154046016963493</v>
       </c>
       <c r="E31">
-        <v>-25.09296035278421</v>
+        <v>-25.75149104297963</v>
       </c>
       <c r="F31">
-        <v>-3.059550298465398</v>
+        <v>-3.18742040423114</v>
       </c>
       <c r="G31">
-        <v>2.656433558771495</v>
+        <v>3.547927056496293</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.154401593406492</v>
       </c>
       <c r="E32">
-        <v>-25.2278001948366</v>
+        <v>-24.52621277377625</v>
       </c>
       <c r="F32">
-        <v>-3.226436508902997</v>
+        <v>-3.397220187970769</v>
       </c>
       <c r="G32">
-        <v>4.188517618345268</v>
+        <v>3.128643153402058</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.189507929113626</v>
       </c>
       <c r="E33">
-        <v>-22.10710195887874</v>
+        <v>-24.54663619155084</v>
       </c>
       <c r="F33">
-        <v>-2.726568968459872</v>
+        <v>-3.409974560871673</v>
       </c>
       <c r="G33">
-        <v>3.220735909213504</v>
+        <v>2.789441346902793</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.258126432581714</v>
       </c>
       <c r="E34">
-        <v>-24.7394269154794</v>
+        <v>-24.57717622025857</v>
       </c>
       <c r="F34">
-        <v>-3.937288398471754</v>
+        <v>-3.644045509513326</v>
       </c>
       <c r="G34">
-        <v>3.51578496985551</v>
+        <v>3.675558518671816</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.365934730571612</v>
       </c>
       <c r="E35">
-        <v>-21.73002045673404</v>
+        <v>-23.30111111505916</v>
       </c>
       <c r="F35">
-        <v>-3.243779208848008</v>
+        <v>-3.23894485668527</v>
       </c>
       <c r="G35">
-        <v>3.593539752936372</v>
+        <v>3.212618451551212</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.522041514365005</v>
       </c>
       <c r="E36">
-        <v>-21.05301812106133</v>
+        <v>-23.53063682013794</v>
       </c>
       <c r="F36">
-        <v>-2.976112991818418</v>
+        <v>-3.298456427637192</v>
       </c>
       <c r="G36">
-        <v>2.324283214270877</v>
+        <v>2.408294928420962</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.717856725217789</v>
       </c>
       <c r="E37">
-        <v>-21.7275162106078</v>
+        <v>-22.81015660551758</v>
       </c>
       <c r="F37">
-        <v>-3.103768550426835</v>
+        <v>-3.340231824127774</v>
       </c>
       <c r="G37">
-        <v>2.292538393094806</v>
+        <v>2.172908519487702</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.948013819134032</v>
       </c>
       <c r="E38">
-        <v>-21.6380697920083</v>
+        <v>-20.73380598826065</v>
       </c>
       <c r="F38">
-        <v>-2.848954453651679</v>
+        <v>-3.450155350111865</v>
       </c>
       <c r="G38">
-        <v>3.522756978761215</v>
+        <v>2.114146336165639</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.214748345514014</v>
       </c>
       <c r="E39">
-        <v>-19.97561264210442</v>
+        <v>-19.41830693140245</v>
       </c>
       <c r="F39">
-        <v>-3.116788000896635</v>
+        <v>-3.359433380524667</v>
       </c>
       <c r="G39">
-        <v>2.130291866760664</v>
+        <v>2.179056202554129</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.506920024902549</v>
       </c>
       <c r="E40">
-        <v>-18.45662207723754</v>
+        <v>-20.24204088187169</v>
       </c>
       <c r="F40">
-        <v>-3.121774772661488</v>
+        <v>-3.261102856342754</v>
       </c>
       <c r="G40">
-        <v>1.743729395776586</v>
+        <v>0.9515886802308546</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.81357294141932</v>
       </c>
       <c r="E41">
-        <v>-18.48888745454219</v>
+        <v>-19.55536119724459</v>
       </c>
       <c r="F41">
-        <v>-2.853709282543749</v>
+        <v>-3.039534456911553</v>
       </c>
       <c r="G41">
-        <v>1.664541146477219</v>
+        <v>0.218623966199596</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.135050609713979</v>
       </c>
       <c r="E42">
-        <v>-17.10165736940249</v>
+        <v>-17.99185573288231</v>
       </c>
       <c r="F42">
-        <v>-3.100658859196726</v>
+        <v>-3.406037330606166</v>
       </c>
       <c r="G42">
-        <v>1.175941040881724</v>
+        <v>1.295402076666325</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.462456633199842</v>
       </c>
       <c r="E43">
-        <v>-16.69832883190933</v>
+        <v>-16.95151581367818</v>
       </c>
       <c r="F43">
-        <v>-2.607411631036774</v>
+        <v>-3.048148649533265</v>
       </c>
       <c r="G43">
-        <v>0.2988484162527547</v>
+        <v>0.7025264076748654</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.783003023127243</v>
       </c>
       <c r="E44">
-        <v>-15.98153932360523</v>
+        <v>-16.63205008633307</v>
       </c>
       <c r="F44">
-        <v>-2.544747293749797</v>
+        <v>-2.80851438541441</v>
       </c>
       <c r="G44">
-        <v>-0.05636649901996514</v>
+        <v>-0.5217762331128657</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.09757163697249</v>
       </c>
       <c r="E45">
-        <v>-14.55604816157472</v>
+        <v>-15.04161378704718</v>
       </c>
       <c r="F45">
-        <v>-2.712239040758843</v>
+        <v>-2.873232245492928</v>
       </c>
       <c r="G45">
-        <v>0.7074756732560759</v>
+        <v>-0.6909881472616339</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.40212915837655</v>
       </c>
       <c r="E46">
-        <v>-14.4524230908572</v>
+        <v>-13.57626299680116</v>
       </c>
       <c r="F46">
-        <v>-2.867395568772802</v>
+        <v>-2.715134184831628</v>
       </c>
       <c r="G46">
-        <v>-0.6352584236535427</v>
+        <v>-0.5557887779833379</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.68400414358047</v>
       </c>
       <c r="E47">
-        <v>-12.86799154810548</v>
+        <v>-13.43237526368144</v>
       </c>
       <c r="F47">
-        <v>-2.508361255581829</v>
+        <v>-2.757713926070328</v>
       </c>
       <c r="G47">
-        <v>-1.480450631466095</v>
+        <v>-1.504521608082135</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.94540660303498</v>
       </c>
       <c r="E48">
-        <v>-10.15213888843335</v>
+        <v>-13.35135633521021</v>
       </c>
       <c r="F48">
-        <v>-2.629524898854507</v>
+        <v>-2.661798092867576</v>
       </c>
       <c r="G48">
-        <v>-0.4434089991072382</v>
+        <v>-1.704346136832544</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.18815538208617</v>
       </c>
       <c r="E49">
-        <v>-10.48828751402272</v>
+        <v>-12.55218935623257</v>
       </c>
       <c r="F49">
-        <v>-2.248856942572022</v>
+        <v>-2.308304729233929</v>
       </c>
       <c r="G49">
-        <v>-0.9799126986559875</v>
+        <v>-1.515989337830171</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.40044161344283</v>
       </c>
       <c r="E50">
-        <v>-10.18925878987423</v>
+        <v>-11.97308810013169</v>
       </c>
       <c r="F50">
-        <v>-2.370149811159537</v>
+        <v>-2.949308679398631</v>
       </c>
       <c r="G50">
-        <v>-0.4770640050594691</v>
+        <v>-1.750673911109105</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.58494128407348</v>
       </c>
       <c r="E51">
-        <v>-8.512170140451564</v>
+        <v>-9.538299708219629</v>
       </c>
       <c r="F51">
-        <v>-2.424266225217026</v>
+        <v>-2.53970005116454</v>
       </c>
       <c r="G51">
-        <v>-2.854585252815701</v>
+        <v>-2.862848374481721</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.74873603662685</v>
       </c>
       <c r="E52">
-        <v>-9.657878592866174</v>
+        <v>-9.021030236219476</v>
       </c>
       <c r="F52">
-        <v>-2.081997239891312</v>
+        <v>-1.934575178317293</v>
       </c>
       <c r="G52">
-        <v>-3.313529491470404</v>
+        <v>-2.887962172942633</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.88030770682872</v>
       </c>
       <c r="E53">
-        <v>-8.058598183843301</v>
+        <v>-8.769355764769188</v>
       </c>
       <c r="F53">
-        <v>-2.443560558763032</v>
+        <v>-2.516161163046589</v>
       </c>
       <c r="G53">
-        <v>-2.684125262998627</v>
+        <v>-3.370215962739345</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.98050778292111</v>
       </c>
       <c r="E54">
-        <v>-6.809857890806178</v>
+        <v>-8.657615668629921</v>
       </c>
       <c r="F54">
-        <v>-2.314389916174894</v>
+        <v>-2.29510800813993</v>
       </c>
       <c r="G54">
-        <v>-2.622118745048077</v>
+        <v>-4.658475032800256</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.05867261148933</v>
       </c>
       <c r="E55">
-        <v>-5.148555501774254</v>
+        <v>-8.658915340670124</v>
       </c>
       <c r="F55">
-        <v>-1.919387061986964</v>
+        <v>-2.147575773701338</v>
       </c>
       <c r="G55">
-        <v>-2.997001611369607</v>
+        <v>-3.569772337301073</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.10561635770947</v>
       </c>
       <c r="E56">
-        <v>-6.089816938164568</v>
+        <v>-7.107577885966458</v>
       </c>
       <c r="F56">
-        <v>-2.461539444873392</v>
+        <v>-2.608306267831798</v>
       </c>
       <c r="G56">
-        <v>-3.306199943646458</v>
+        <v>-3.871482215568092</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.12038482807588</v>
       </c>
       <c r="E57">
-        <v>-4.120030371256131</v>
+        <v>-6.921856109963882</v>
       </c>
       <c r="F57">
-        <v>-2.642914629553359</v>
+        <v>-2.319529935909265</v>
       </c>
       <c r="G57">
-        <v>-3.177121773070274</v>
+        <v>-4.242644028703481</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.11402375271814</v>
       </c>
       <c r="E58">
-        <v>-5.199953681761312</v>
+        <v>-5.081959763017453</v>
       </c>
       <c r="F58">
-        <v>-2.148365207836206</v>
+        <v>-2.234850078158086</v>
       </c>
       <c r="G58">
-        <v>-4.473087793146608</v>
+        <v>-4.176621819013795</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.0820334387939</v>
       </c>
       <c r="E59">
-        <v>-3.485654561417622</v>
+        <v>-5.770396495559532</v>
       </c>
       <c r="F59">
-        <v>-1.994845533810179</v>
+        <v>-2.727944058348519</v>
       </c>
       <c r="G59">
-        <v>-4.096278189321223</v>
+        <v>-5.082334109829764</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.02007467120751</v>
       </c>
       <c r="E60">
-        <v>-2.822925975817088</v>
+        <v>-5.17783661470785</v>
       </c>
       <c r="F60">
-        <v>-2.304638375109138</v>
+        <v>-2.269547075191745</v>
       </c>
       <c r="G60">
-        <v>-3.308772237530472</v>
+        <v>-4.829474641540231</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.93742015178787</v>
       </c>
       <c r="E61">
-        <v>-5.009295869090375</v>
+        <v>-5.002946948531621</v>
       </c>
       <c r="F61">
-        <v>-2.274595146144406</v>
+        <v>-2.472202190082228</v>
       </c>
       <c r="G61">
-        <v>-3.980074730347265</v>
+        <v>-5.246182940204913</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.83217465053092</v>
       </c>
       <c r="E62">
-        <v>-1.134344059362957</v>
+        <v>-4.31045270327867</v>
       </c>
       <c r="F62">
-        <v>-2.767173881810298</v>
+        <v>-2.073231456034888</v>
       </c>
       <c r="G62">
-        <v>-4.199375198505206</v>
+        <v>-4.691808915835177</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.69731251196691</v>
       </c>
       <c r="E63">
-        <v>-3.623542066477177</v>
+        <v>-4.23748087311907</v>
       </c>
       <c r="F63">
-        <v>-3.173238754295213</v>
+        <v>-2.082816495252681</v>
       </c>
       <c r="G63">
-        <v>-4.93631587772913</v>
+        <v>-4.745645007394805</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.54047934231053</v>
       </c>
       <c r="E64">
-        <v>-1.847922879595622</v>
+        <v>-2.910791956987916</v>
       </c>
       <c r="F64">
-        <v>-2.830867051411552</v>
+        <v>-2.510090058351472</v>
       </c>
       <c r="G64">
-        <v>-4.530827017897038</v>
+        <v>-4.932978847825544</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.36396433914602</v>
       </c>
       <c r="E65">
-        <v>-1.918494618531157</v>
+        <v>-3.548559593858171</v>
       </c>
       <c r="F65">
-        <v>-2.80251037847892</v>
+        <v>-2.311112894729419</v>
       </c>
       <c r="G65">
-        <v>-4.695003592280575</v>
+        <v>-5.198822275720099</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.1606492897347</v>
       </c>
       <c r="E66">
-        <v>-0.779882284886568</v>
+        <v>-3.047117138514825</v>
       </c>
       <c r="F66">
-        <v>-2.728465929812283</v>
+        <v>-2.308138227385966</v>
       </c>
       <c r="G66">
-        <v>-3.928867211945819</v>
+        <v>-4.693136444596425</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.93595476951238</v>
       </c>
       <c r="E67">
-        <v>-1.2651399741265</v>
+        <v>-3.202480024769979</v>
       </c>
       <c r="F67">
-        <v>-2.784322743783054</v>
+        <v>-2.746421621635365</v>
       </c>
       <c r="G67">
-        <v>-3.020708427976329</v>
+        <v>-4.561499222318385</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.69546462144769</v>
       </c>
       <c r="E68">
-        <v>-0.3025086688939895</v>
+        <v>-3.190434283909576</v>
       </c>
       <c r="F68">
-        <v>-2.787856559123396</v>
+        <v>-2.573556255284358</v>
       </c>
       <c r="G68">
-        <v>-2.439217725094423</v>
+        <v>-4.195180737306949</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.43132924021986</v>
       </c>
       <c r="E69">
-        <v>-0.5789810640102802</v>
+        <v>-2.920831583862921</v>
       </c>
       <c r="F69">
-        <v>-2.805552143581999</v>
+        <v>-2.417551479049934</v>
       </c>
       <c r="G69">
-        <v>-3.702356375603344</v>
+        <v>-4.347886271396912</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.1437849385248</v>
       </c>
       <c r="E70">
-        <v>-1.923987657502461</v>
+        <v>-1.889648239102296</v>
       </c>
       <c r="F70">
-        <v>-2.770144407316737</v>
+        <v>-2.343461470176143</v>
       </c>
       <c r="G70">
-        <v>-4.288743375337832</v>
+        <v>-4.609972230104394</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.839224624152495</v>
       </c>
       <c r="E71">
-        <v>-1.486206489758944</v>
+        <v>-2.431077119933372</v>
       </c>
       <c r="F71">
-        <v>-2.698943743943911</v>
+        <v>-2.724297585041396</v>
       </c>
       <c r="G71">
-        <v>-3.408684501905676</v>
+        <v>-3.459474891569175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.508829806628956</v>
       </c>
       <c r="E72">
-        <v>-2.678109905525798</v>
+        <v>-3.351761170432833</v>
       </c>
       <c r="F72">
-        <v>-2.849136694480295</v>
+        <v>-2.597322116070676</v>
       </c>
       <c r="G72">
-        <v>-2.979247155642496</v>
+        <v>-3.467814155782599</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.147134427763806</v>
       </c>
       <c r="E73">
-        <v>-2.897922033858117</v>
+        <v>-3.032408654937911</v>
       </c>
       <c r="F73">
-        <v>-3.177203320685011</v>
+        <v>-2.493675958264999</v>
       </c>
       <c r="G73">
-        <v>-2.496887428388527</v>
+        <v>-2.966190364035611</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.762023796791643</v>
       </c>
       <c r="E74">
-        <v>-1.036039945604449</v>
+        <v>-3.665050059231483</v>
       </c>
       <c r="F74">
-        <v>-3.185034706111078</v>
+        <v>-2.477033228775355</v>
       </c>
       <c r="G74">
-        <v>-3.174420367910229</v>
+        <v>-2.742205473939601</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.346935583984529</v>
       </c>
       <c r="E75">
-        <v>-3.937935902933699</v>
+        <v>-3.670081193854005</v>
       </c>
       <c r="F75">
-        <v>-3.374652146448899</v>
+        <v>-2.130800505427245</v>
       </c>
       <c r="G75">
-        <v>-2.439376631280308</v>
+        <v>-2.535014981364313</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.897497029723731</v>
       </c>
       <c r="E76">
-        <v>-2.0334091749498</v>
+        <v>-5.214743677870364</v>
       </c>
       <c r="F76">
-        <v>-3.111756497292031</v>
+        <v>-2.53994856138538</v>
       </c>
       <c r="G76">
-        <v>-0.9839912907603696</v>
+        <v>-1.853976174116523</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.425118862638566</v>
       </c>
       <c r="E77">
-        <v>-5.20845362747371</v>
+        <v>-4.094344866684625</v>
       </c>
       <c r="F77">
-        <v>-3.232375074813667</v>
+        <v>-2.83276318439656</v>
       </c>
       <c r="G77">
-        <v>-1.458541441087198</v>
+        <v>-1.702263803688343</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.931722072230522</v>
       </c>
       <c r="E78">
-        <v>-4.09771857982034</v>
+        <v>-6.413159039260247</v>
       </c>
       <c r="F78">
-        <v>-3.415873365147008</v>
+        <v>-3.234744205585673</v>
       </c>
       <c r="G78">
-        <v>-0.5275398928967369</v>
+        <v>-1.31817099967656</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.418452144888231</v>
       </c>
       <c r="E79">
-        <v>-4.625575624050427</v>
+        <v>-5.442009674419308</v>
       </c>
       <c r="F79">
-        <v>-3.455948123359642</v>
+        <v>-3.240361364944057</v>
       </c>
       <c r="G79">
-        <v>0.1861475144593457</v>
+        <v>-1.388374428382345</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.900180445631497</v>
       </c>
       <c r="E80">
-        <v>-4.649467852914896</v>
+        <v>-6.118310096620831</v>
       </c>
       <c r="F80">
-        <v>-3.445499925308132</v>
+        <v>-2.704152518172715</v>
       </c>
       <c r="G80">
-        <v>1.26798744905562</v>
+        <v>-0.5217861647494835</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.385356540401142</v>
       </c>
       <c r="E81">
-        <v>-5.88213206322479</v>
+        <v>-6.500200838161679</v>
       </c>
       <c r="F81">
-        <v>-3.895870028331779</v>
+        <v>-3.093165447671002</v>
       </c>
       <c r="G81">
-        <v>1.255529866191342</v>
+        <v>-0.4721776398435048</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.87872702449018</v>
       </c>
       <c r="E82">
-        <v>-6.826663057848643</v>
+        <v>-8.769038771588651</v>
       </c>
       <c r="F82">
-        <v>-3.599865362452417</v>
+        <v>-2.703910634891097</v>
       </c>
       <c r="G82">
-        <v>1.194235115531736</v>
+        <v>0.6168561102096056</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.39662701250569</v>
       </c>
       <c r="E83">
-        <v>-9.304173073549064</v>
+        <v>-8.712296992272542</v>
       </c>
       <c r="F83">
-        <v>-3.923869674913805</v>
+        <v>-3.322797175401053</v>
       </c>
       <c r="G83">
-        <v>2.61430024569319</v>
+        <v>1.677515174445623</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.953862488778954</v>
       </c>
       <c r="E84">
-        <v>-8.994728859182926</v>
+        <v>-10.3144031690762</v>
       </c>
       <c r="F84">
-        <v>-3.545221278359345</v>
+        <v>-3.35549615025916</v>
       </c>
       <c r="G84">
-        <v>1.443075581536594</v>
+        <v>1.214409580048055</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.561042536405914</v>
       </c>
       <c r="E85">
-        <v>-10.64771696993677</v>
+        <v>-11.24103763442174</v>
       </c>
       <c r="F85">
-        <v>-4.182101615592911</v>
+        <v>-3.460388172638648</v>
       </c>
       <c r="G85">
-        <v>2.639778204163421</v>
+        <v>2.422954024068855</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.237856710657479</v>
       </c>
       <c r="E86">
-        <v>-13.55332627595231</v>
+        <v>-12.49886204631825</v>
       </c>
       <c r="F86">
-        <v>-4.086003541561544</v>
+        <v>-3.755846944399564</v>
       </c>
       <c r="G86">
-        <v>1.471791253544233</v>
+        <v>2.748781226589465</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.001679900441467</v>
       </c>
       <c r="E87">
-        <v>-13.95791825769361</v>
+        <v>-13.68952918868101</v>
       </c>
       <c r="F87">
-        <v>-3.828580087467569</v>
+        <v>-3.701096829278934</v>
       </c>
       <c r="G87">
-        <v>3.202733162570948</v>
+        <v>2.573904969023003</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.858128111966614</v>
       </c>
       <c r="E88">
-        <v>-13.79489772189148</v>
+        <v>-15.00058581253768</v>
       </c>
       <c r="F88">
-        <v>-4.04006145703488</v>
+        <v>-3.423364291570524</v>
       </c>
       <c r="G88">
-        <v>3.070847649377462</v>
+        <v>3.262776527016709</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.817117508234897</v>
       </c>
       <c r="E89">
-        <v>-17.59034311346623</v>
+        <v>-16.12241562150984</v>
       </c>
       <c r="F89">
-        <v>-4.480929357581013</v>
+        <v>-3.865839224878088</v>
       </c>
       <c r="G89">
-        <v>3.789894829961625</v>
+        <v>2.917834234552348</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.886557934731187</v>
       </c>
       <c r="E90">
-        <v>-17.86417993671006</v>
+        <v>-16.68202632548172</v>
       </c>
       <c r="F90">
-        <v>-4.48584323301442</v>
+        <v>-3.624315454713448</v>
       </c>
       <c r="G90">
-        <v>2.663660479683724</v>
+        <v>3.313682785774082</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.058672480436266</v>
       </c>
       <c r="E91">
-        <v>-20.0002248983361</v>
+        <v>-19.62429815706336</v>
       </c>
       <c r="F91">
-        <v>-4.546568362211444</v>
+        <v>-3.945259777988893</v>
       </c>
       <c r="G91">
-        <v>3.733357333241951</v>
+        <v>3.14544417201386</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.331663772293049</v>
       </c>
       <c r="E92">
-        <v>-20.96636577092456</v>
+        <v>-21.74426250748817</v>
       </c>
       <c r="F92">
-        <v>-3.904946449964253</v>
+        <v>-3.563252351616082</v>
       </c>
       <c r="G92">
-        <v>2.591378028379277</v>
+        <v>2.894590894321125</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.70378947249811</v>
       </c>
       <c r="E93">
-        <v>-23.17584899553299</v>
+        <v>-23.91996784447339</v>
       </c>
       <c r="F93">
-        <v>-4.015577401710336</v>
+        <v>-3.621981115372359</v>
       </c>
       <c r="G93">
-        <v>2.098278891395912</v>
+        <v>3.274965955692306</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.156765540224875</v>
       </c>
       <c r="E94">
-        <v>-25.39292194257829</v>
+        <v>-25.64029436372129</v>
       </c>
       <c r="F94">
-        <v>-3.795992113841437</v>
+        <v>-3.872534090227514</v>
       </c>
       <c r="G94">
-        <v>1.393625962816501</v>
+        <v>2.994675307064371</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.68003240409374</v>
       </c>
       <c r="E95">
-        <v>-27.62851634831495</v>
+        <v>-27.31571200623512</v>
       </c>
       <c r="F95">
-        <v>-4.395603373255651</v>
+        <v>-4.306170343347207</v>
       </c>
       <c r="G95">
-        <v>1.611188394566325</v>
+        <v>2.176003879566921</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.269131014572677</v>
       </c>
       <c r="E96">
-        <v>-30.42772236480926</v>
+        <v>-28.973445957749</v>
       </c>
       <c r="F96">
-        <v>-4.929547463547739</v>
+        <v>-4.319186480347396</v>
       </c>
       <c r="G96">
-        <v>0.655619287928932</v>
+        <v>2.529364889337649</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.895200620728874</v>
       </c>
       <c r="E97">
-        <v>-31.15955546376685</v>
+        <v>-32.0501840322774</v>
       </c>
       <c r="F97">
-        <v>-4.768950218432193</v>
+        <v>-4.470507667286393</v>
       </c>
       <c r="G97">
-        <v>-0.1689018735364106</v>
+        <v>2.462028393068873</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.556845389989076</v>
       </c>
       <c r="E98">
-        <v>-36.00944244260562</v>
+        <v>-34.374885221063</v>
       </c>
       <c r="F98">
-        <v>-4.295795041627144</v>
+        <v>-4.507898515113957</v>
       </c>
       <c r="G98">
-        <v>0.250852127024401</v>
+        <v>0.8963025697250258</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.222395605367009</v>
       </c>
       <c r="E99">
-        <v>-36.38053050940117</v>
+        <v>-35.99444640092921</v>
       </c>
       <c r="F99">
-        <v>-5.11919472511206</v>
+        <v>-4.471724539001105</v>
       </c>
       <c r="G99">
-        <v>-0.1054983053682888</v>
+        <v>1.761093207130063</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.90409811501042</v>
       </c>
       <c r="E100">
-        <v>-39.80081673604747</v>
+        <v>-38.81489775323051</v>
       </c>
       <c r="F100">
-        <v>-4.748530133585782</v>
+        <v>-4.627118808459667</v>
       </c>
       <c r="G100">
-        <v>-0.6849265383792283</v>
+        <v>0.1632286076909712</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.534319945922919</v>
       </c>
       <c r="E101">
-        <v>-42.89399317122371</v>
+        <v>-40.53018860938188</v>
       </c>
       <c r="F101">
-        <v>-4.944398434345128</v>
+        <v>-4.614810925588873</v>
       </c>
       <c r="G101">
-        <v>-0.6986785445493608</v>
+        <v>0.6722878847191623</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.190433958916108</v>
       </c>
       <c r="E102">
-        <v>-44.16614567488049</v>
+        <v>-43.32009993297545</v>
       </c>
       <c r="F102">
-        <v>-5.174238910660685</v>
+        <v>-4.881072231503315</v>
       </c>
       <c r="G102">
-        <v>-1.680592972588274</v>
+        <v>0.006391512767998748</v>
       </c>
     </row>
   </sheetData>
